--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
@@ -1,37 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D187544A3084281E03535C3088B35299F688" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D6028A0-3284-4473-BEB0-0BF727736946}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sinais_Aprovados" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Hora</t>
+  </si>
+  <si>
+    <t>Liga</t>
+  </si>
+  <si>
+    <t>Jogo</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Away</t>
+  </si>
+  <si>
+    <t>Método</t>
+  </si>
+  <si>
+    <t>Mercado</t>
+  </si>
+  <si>
+    <t>Lado</t>
+  </si>
+  <si>
+    <t>Odd_Entrada</t>
+  </si>
+  <si>
+    <t>Odd_Fav</t>
+  </si>
+  <si>
+    <t>Stake_Sugerida_R$</t>
+  </si>
+  <si>
+    <t>Risco_Red_R$</t>
+  </si>
+  <si>
+    <t>Placar</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
+    <t>1/0</t>
+  </si>
+  <si>
+    <t>P/L</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>COLOMBIA 1</t>
+  </si>
+  <si>
+    <t>Ind Medellin x Jaguares de Cordoba</t>
+  </si>
+  <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
+    <t>Jaguares de Cordoba</t>
+  </si>
+  <si>
+    <t>Lay Draw (Fav &lt;= 1.40)</t>
+  </si>
+  <si>
+    <t>Match Odds (Draw)</t>
+  </si>
+  <si>
+    <t>LAY</t>
+  </si>
+  <si>
+    <t>PENDENTE</t>
+  </si>
+  <si>
+    <t>⏳ PENDENTE</t>
+  </si>
+  <si>
+    <t>2x1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +147,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,148 +471,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Liga</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Jogo</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Método</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Mercado</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Lado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Entrada</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Fav</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Placar</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>COLOMBIA 1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ind Medellin x Jaguares de Cordoba</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Ind Medellin</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Jaguares de Cordoba</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2">
+        <v>6.2</v>
+      </c>
+      <c r="K2">
+        <v>1.33</v>
+      </c>
+      <c r="L2">
+        <v>19.23</v>
+      </c>
+      <c r="M2">
+        <v>100</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D187544A3084281E03535C3088B35299F688" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D6028A0-3284-4473-BEB0-0BF727736946}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D187544A3084281E03535C3088B35299F688" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5089251B-E859-4DBD-8F68-AD690C49DE55}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,6 +474,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
@@ -1,138 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D187544A3084281E03535C3088B35299F688" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5089251B-E859-4DBD-8F68-AD690C49DE55}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sinais_Aprovados" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Hora</t>
-  </si>
-  <si>
-    <t>Liga</t>
-  </si>
-  <si>
-    <t>Jogo</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Away</t>
-  </si>
-  <si>
-    <t>Método</t>
-  </si>
-  <si>
-    <t>Mercado</t>
-  </si>
-  <si>
-    <t>Lado</t>
-  </si>
-  <si>
-    <t>Odd_Entrada</t>
-  </si>
-  <si>
-    <t>Odd_Fav</t>
-  </si>
-  <si>
-    <t>Stake_Sugerida_R$</t>
-  </si>
-  <si>
-    <t>Risco_Red_R$</t>
-  </si>
-  <si>
-    <t>Placar</t>
-  </si>
-  <si>
-    <t>Resultado</t>
-  </si>
-  <si>
-    <t>1/0</t>
-  </si>
-  <si>
-    <t>P/L</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>2026-09-22</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>COLOMBIA 1</t>
-  </si>
-  <si>
-    <t>Ind Medellin x Jaguares de Cordoba</t>
-  </si>
-  <si>
-    <t>Ind Medellin</t>
-  </si>
-  <si>
-    <t>Jaguares de Cordoba</t>
-  </si>
-  <si>
-    <t>Lay Draw (Fav &lt;= 1.40)</t>
-  </si>
-  <si>
-    <t>Match Odds (Draw)</t>
-  </si>
-  <si>
-    <t>LAY</t>
-  </si>
-  <si>
-    <t>PENDENTE</t>
-  </si>
-  <si>
-    <t>⏳ PENDENTE</t>
-  </si>
-  <si>
-    <t>2x1</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -147,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -471,117 +420,1250 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Liga</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Jogo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Método</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mercado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Entrada</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Fav</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Placar</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Origem</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Liquidez_Lay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bhutan Premier League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RTC FC x Tsirang FC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RTC FC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tsirang FC</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Other Competitions Soccer</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>South Korea U23 x Saudi Arabia U23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>South Korea U23</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia U23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Romanian Liga III</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SC FC Voluntari SA II x ACS LPS HD Clinceni</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SC FC Voluntari SA II</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ACS LPS HD Clinceni</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Romanian Liga III</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CSO Plopeni x CS Blejoi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CSO Plopeni</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CS Blejoi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Romanian Liga III</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ACSO Filiasi x CS Uni Craiova II</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ACSO Filiasi</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CS Uni Craiova II</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="K6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Uzbekistan 1st Division</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TerDU x Gazalkent</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TerDU</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gazalkent</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Romanian Liga III</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CSO Plopeni x CS Blejoi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CSO Plopeni</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CS Blejoi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Romanian Liga III</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ACSO Filiasi x CS Uni Craiova II</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ACSO Filiasi</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CS Uni Craiova II</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dutch Cup</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ACV Assen x Hoogeveen</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ACV Assen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Hoogeveen</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dutch Cup</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Excelsior '31 x AFC '34</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Excelsior '31</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AFC '34</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="K11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dutch Cup</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Groene Ster x AFC Amsterdam</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groene Ster</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AFC Amsterdam</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Scottish Challenge Cup</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gala Fairydean x Spartans</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Gala Fairydean</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spartans</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Scottish Challenge Cup</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>East Kilbride x Celtic B</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>East Kilbride</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Celtic B</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Scottish Challenge Cup</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fraserburgh x Cove Rangers</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fraserburgh</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cove Rangers</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Scottish Challenge Cup</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Berwick x Stranraer</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Berwick</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stranraer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chilean Cup</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Puerto Montt x Nublense</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nublense</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2">
-        <v>6.2</v>
-      </c>
-      <c r="K2">
-        <v>1.33</v>
-      </c>
-      <c r="L2">
-        <v>19.23</v>
-      </c>
-      <c r="M2">
-        <v>100</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" t="s">
-        <v>28</v>
+      <c r="K17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ind Medellin x Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1523</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,27 +518,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bhutan Premier League</t>
+          <t>Dutch Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RTC FC x Tsirang FC</t>
+          <t>ACV Assen x Hoogeveen</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RTC FC</t>
+          <t>ACV Assen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tsirang FC</t>
+          <t>Hoogeveen</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="K2" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>175</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3">
@@ -586,27 +586,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other Competitions Soccer</t>
+          <t>Dutch Cup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>South Korea U23 x Saudi Arabia U23</t>
+          <t>Excelsior '31 x AFC '34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>South Korea U23</t>
+          <t>Excelsior '31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia U23</t>
+          <t>AFC '34</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>377</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4">
@@ -654,32 +654,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romanian Liga III</t>
+          <t>Dutch Cup</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SC FC Voluntari SA II x ACS LPS HD Clinceni</t>
+          <t>Groene Ster x AFC Amsterdam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SC FC Voluntari SA II</t>
+          <t>Groene Ster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ACS LPS HD Clinceni</t>
+          <t>AFC Amsterdam</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>137</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5">
@@ -722,27 +722,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romanian Liga III</t>
+          <t>Scottish Challenge Cup</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSO Plopeni x CS Blejoi</t>
+          <t>Gala Fairydean x Spartans</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CSO Plopeni</t>
+          <t>Gala Fairydean</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Blejoi</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -790,27 +790,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romanian Liga III</t>
+          <t>Scottish Challenge Cup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ACSO Filiasi x CS Uni Craiova II</t>
+          <t>East Kilbride x Celtic B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ACSO Filiasi</t>
+          <t>East Kilbride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Uni Craiova II</t>
+          <t>Celtic B</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="K6" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
@@ -858,27 +858,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan 1st Division</t>
+          <t>Scottish Challenge Cup</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TerDU x Gazalkent</t>
+          <t>Fraserburgh x Cove Rangers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TerDU</t>
+          <t>Fraserburgh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gazalkent</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
@@ -926,27 +926,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romanian Liga III</t>
+          <t>Scottish Challenge Cup</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSO Plopeni x CS Blejoi</t>
+          <t>Berwick x Stranraer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CSO Plopeni</t>
+          <t>Berwick</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Blejoi</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
@@ -994,32 +994,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romanian Liga III</t>
+          <t>Chilean Cup</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ACSO Filiasi x CS Uni Craiova II</t>
+          <t>Puerto Montt x Nublense</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ACSO Filiasi</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Uni Craiova II</t>
+          <t>Nublense</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>1.47</v>
+        <v>2.58</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>135</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10">
@@ -1062,27 +1062,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dutch Cup</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ACV Assen x Hoogeveen</t>
+          <t>Ind Medellin x Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ACV Assen</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hoogeveen</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1119,550 +1119,6 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dutch Cup</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Excelsior '31 x AFC '34</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Excelsior '31</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AFC '34</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dutch Cup</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Groene Ster x AFC Amsterdam</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Groene Ster</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AFC Amsterdam</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Scottish Challenge Cup</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Gala Fairydean x Spartans</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Gala Fairydean</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Spartans</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Scottish Challenge Cup</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>East Kilbride x Celtic B</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>East Kilbride</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Celtic B</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Scottish Challenge Cup</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fraserburgh x Cove Rangers</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Fraserburgh</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Cove Rangers</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Scottish Challenge Cup</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Berwick x Stranraer</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Berwick</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Stranraer</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chilean Cup</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Puerto Montt x Nublense</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Nublense</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ind Medellin x Jaguares de Cordoba</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Ind Medellin</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Jaguares de Cordoba</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
         <v>1523</v>
       </c>
     </row>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,32 +994,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chilean Cup</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Puerto Montt x Nublense</t>
+          <t>Ind Medellin x Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nublense</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.58</v>
+        <v>1.35</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
@@ -1051,74 +1051,6 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ind Medellin x Jaguares de Cordoba</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ind Medellin</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Jaguares de Cordoba</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
         <v>1523</v>
       </c>
     </row>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-22.xlsx
@@ -558,15 +558,19 @@
       <c r="K2" t="n">
         <v>1.31</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -626,15 +630,19 @@
       <c r="K3" t="n">
         <v>1.31</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4x3</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -697,12 +705,12 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>SEM_PLACAR</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>⚪ SEM_PLACAR</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -762,15 +770,19 @@
       <c r="K5" t="n">
         <v>1.29</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -830,15 +842,19 @@
       <c r="K6" t="n">
         <v>1.26</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1x5</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -901,12 +917,12 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>SEM_PLACAR</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>⚪ SEM_PLACAR</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -966,15 +982,19 @@
       <c r="K8" t="n">
         <v>1.55</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3x2</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1034,15 +1054,19 @@
       <c r="K9" t="n">
         <v>1.35</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
